--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$110</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3805" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4065" uniqueCount="584">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -854,7 +854,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -879,28 +879,19 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-vaccine-code-cis|0.1.0</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:translation</t>
-  </si>
-  <si>
-    <t>translation</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.id</t>
+    <t>Immunization.vaccineCode.coding:cis.id</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.id</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:translation.extension</t>
+    <t>Immunization.vaccineCode.coding:cis.extension</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.extension</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:translation.system</t>
+    <t>Immunization.vaccineCode.coding:cis.system</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.system</t>
@@ -918,6 +909,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/terminologie-bdpm</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -927,7 +921,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:translation.version</t>
+    <t>Immunization.vaccineCode.coding:cis.version</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.version</t>
@@ -951,7 +945,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:translation.code</t>
+    <t>Immunization.vaccineCode.coding:cis.code</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.code</t>
@@ -975,7 +969,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:translation.display</t>
+    <t>Immunization.vaccineCode.coding:cis.display</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.display</t>
@@ -999,7 +993,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:translation.userSelected</t>
+    <t>Immunization.vaccineCode.coding:cis.userSelected</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.userSelected</t>
@@ -1030,6 +1024,36 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
+    <t>Immunization.vaccineCode.coding:translation</t>
+  </si>
+  <si>
+    <t>translation</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.id</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.system</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.version</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.code</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.display</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.userSelected</t>
+  </si>
+  <si>
     <t>Immunization.vaccineCode.text</t>
   </si>
   <si>
@@ -1285,7 +1309,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260916095452</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1306,7 +1330,7 @@
     <t>The path by which the vaccine product is taken into the body.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260916095454</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1731,7 +1755,7 @@
     <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260716085853</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260916095457</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.authority</t>
@@ -2114,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO103"/>
+  <dimension ref="A1:AO110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.0" customWidth="true" bestFit="true"/>
@@ -7167,11 +7191,9 @@
         <v>277</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C44" t="s" s="2">
         <v>278</v>
       </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7180,7 +7202,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7189,23 +7211,19 @@
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>264</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>150</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7229,11 +7247,13 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7251,28 +7271,28 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>271</v>
+        <v>152</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>273</v>
+        <v>153</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7283,21 +7303,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7309,15 +7329,17 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7354,31 +7376,31 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
@@ -7398,21 +7420,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>78</v>
@@ -7421,21 +7443,23 @@
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7444,7 +7468,7 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>78</v>
@@ -7471,40 +7495,40 @@
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>153</v>
+        <v>290</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7515,10 +7539,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7526,7 +7550,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -7541,20 +7565,18 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7602,7 +7624,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7620,10 +7642,10 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7634,10 +7656,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7660,18 +7682,18 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7719,7 +7741,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7737,10 +7759,10 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7751,10 +7773,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7777,17 +7799,17 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7836,7 +7858,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7854,10 +7876,10 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7868,10 +7890,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7894,17 +7916,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>149</v>
+        <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7953,7 +7977,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7971,10 +7995,10 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7985,12 +8009,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7999,7 +8025,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>78</v>
@@ -8011,19 +8037,19 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>319</v>
+        <v>264</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>320</v>
+        <v>265</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>321</v>
+        <v>266</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>322</v>
+        <v>267</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>323</v>
+        <v>268</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8048,13 +8074,11 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>78</v>
+        <v>327</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8072,13 +8096,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -8090,10 +8114,10 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8104,10 +8128,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8127,23 +8151,19 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>149</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>328</v>
+        <v>150</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8191,7 +8211,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>332</v>
+        <v>152</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8203,16 +8223,16 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>333</v>
+        <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>334</v>
+        <v>153</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8223,21 +8243,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -8246,18 +8266,20 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>336</v>
+        <v>134</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>337</v>
+        <v>261</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8294,43 +8316,43 @@
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>158</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>340</v>
+        <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>341</v>
+        <v>153</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8338,10 +8360,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>343</v>
+        <v>282</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8349,7 +8371,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8361,19 +8383,23 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>344</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>345</v>
+        <v>283</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8421,7 +8447,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8436,27 +8462,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>348</v>
+        <v>289</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>349</v>
+        <v>290</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8464,13 +8490,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
@@ -8479,16 +8505,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>352</v>
+        <v>149</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>354</v>
+        <v>294</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8538,10 +8564,10 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>89</v>
@@ -8553,27 +8579,27 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>356</v>
+        <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>357</v>
+        <v>297</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>359</v>
+        <v>78</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>360</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8593,19 +8619,21 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>352</v>
+        <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>362</v>
+        <v>301</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8653,7 +8681,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>361</v>
+        <v>304</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8671,13 +8699,13 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>364</v>
+        <v>306</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8685,10 +8713,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
+        <v>308</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8711,18 +8739,18 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>319</v>
+        <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>367</v>
+        <v>309</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8770,7 +8798,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>366</v>
+        <v>312</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8788,13 +8816,13 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>370</v>
+        <v>313</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>371</v>
+        <v>314</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>372</v>
+        <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8802,10 +8830,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>316</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8825,21 +8853,23 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>186</v>
+        <v>317</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>374</v>
+        <v>318</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8863,13 +8893,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>377</v>
+        <v>78</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8887,7 +8917,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>373</v>
+        <v>322</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8905,13 +8935,13 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>370</v>
+        <v>323</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>379</v>
+        <v>324</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>372</v>
+        <v>78</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -8919,10 +8949,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8942,19 +8972,23 @@
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>381</v>
+        <v>149</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9002,7 +9036,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9017,16 +9051,16 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>385</v>
+        <v>341</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -9034,10 +9068,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9045,7 +9079,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>89</v>
@@ -9057,16 +9091,16 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9117,10 +9151,10 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>89</v>
@@ -9132,27 +9166,27 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>347</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>394</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9166,7 +9200,7 @@
         <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>78</v>
@@ -9175,13 +9209,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>149</v>
+        <v>352</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>396</v>
+        <v>353</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>397</v>
+        <v>354</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9232,7 +9266,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9247,27 +9281,27 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>78</v>
+        <v>355</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>399</v>
+        <v>357</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>78</v>
+        <v>358</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>359</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>359</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9275,7 +9309,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>89</v>
@@ -9287,18 +9321,20 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>402</v>
+        <v>360</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>403</v>
+        <v>361</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9347,10 +9383,10 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>359</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>89</v>
@@ -9362,27 +9398,27 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>78</v>
+        <v>368</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9396,7 +9432,7 @@
         <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>78</v>
@@ -9405,13 +9441,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>186</v>
+        <v>360</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>408</v>
+        <v>370</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>409</v>
+        <v>371</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9438,11 +9474,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9460,7 +9498,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9478,24 +9516,24 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>413</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>414</v>
+        <v>374</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>374</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9509,24 +9547,26 @@
         <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J64" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K64" t="s" s="2">
-        <v>186</v>
+        <v>317</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9551,11 +9591,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9573,7 +9615,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>414</v>
+        <v>374</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9591,24 +9633,24 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>418</v>
+        <v>378</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>419</v>
+        <v>379</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9622,7 +9664,7 @@
         <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
@@ -9631,15 +9673,17 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>422</v>
+        <v>186</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>423</v>
+        <v>382</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9664,13 +9708,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>385</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9688,7 +9732,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9706,13 +9750,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>426</v>
+        <v>387</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9720,10 +9764,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>427</v>
+        <v>388</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>427</v>
+        <v>388</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9734,7 +9778,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9743,16 +9787,16 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9803,13 +9847,13 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>427</v>
+        <v>388</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
@@ -9818,16 +9862,16 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>432</v>
+        <v>393</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>433</v>
+        <v>394</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>78</v>
+        <v>395</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9835,10 +9879,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9861,13 +9905,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>149</v>
+        <v>397</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>150</v>
+        <v>398</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>151</v>
+        <v>399</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9918,7 +9962,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>152</v>
+        <v>396</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9930,44 +9974,44 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>153</v>
+        <v>401</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>78</v>
@@ -9976,17 +10020,15 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>261</v>
+        <v>404</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10035,78 +10077,74 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>158</v>
+        <v>403</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>153</v>
+        <v>407</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>134</v>
+        <v>410</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10154,28 +10192,28 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>132</v>
+        <v>414</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10184,12 +10222,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10203,22 +10241,22 @@
         <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>186</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10230,7 +10268,7 @@
         <v>78</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>78</v>
@@ -10245,13 +10283,11 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10269,7 +10305,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10284,27 +10320,27 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>78</v>
+        <v>421</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10312,32 +10348,30 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>451</v>
+        <v>186</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10362,13 +10396,11 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10386,10 +10418,10 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>89</v>
@@ -10401,27 +10433,27 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>455</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>78</v>
+        <v>426</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>456</v>
+        <v>427</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>78</v>
+        <v>428</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10432,7 +10464,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>90</v>
@@ -10441,16 +10473,16 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>460</v>
+        <v>431</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10501,13 +10533,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -10516,13 +10548,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>463</v>
+        <v>433</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10533,10 +10565,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10556,16 +10588,16 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>186</v>
+        <v>436</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10592,13 +10624,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10616,7 +10648,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10631,13 +10663,13 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10646,12 +10678,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10662,10 +10694,10 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>78</v>
@@ -10674,13 +10706,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>473</v>
+        <v>149</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>474</v>
+        <v>150</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>475</v>
+        <v>151</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10731,28 +10763,28 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>472</v>
+        <v>152</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>476</v>
+        <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10763,50 +10795,48 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>319</v>
+        <v>134</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>478</v>
+        <v>261</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>479</v>
+        <v>262</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>480</v>
+        <v>219</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q75" t="s" s="2">
-        <v>481</v>
-      </c>
+      <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10850,28 +10880,28 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>477</v>
+        <v>158</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>482</v>
+        <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10882,14 +10912,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10902,22 +10932,26 @@
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>484</v>
+        <v>446</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10941,13 +10975,13 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>487</v>
+        <v>78</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -10965,7 +10999,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10977,7 +11011,7 @@
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -10997,10 +11031,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11011,7 +11045,7 @@
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11020,16 +11054,16 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>428</v>
+        <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11041,7 +11075,7 @@
         <v>78</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>78</v>
@@ -11056,13 +11090,13 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -11080,28 +11114,28 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>491</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>132</v>
+        <v>457</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11112,10 +11146,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11123,7 +11157,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -11135,18 +11169,20 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>149</v>
+        <v>459</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>150</v>
+        <v>460</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11195,10 +11231,10 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>152</v>
+        <v>458</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>89</v>
@@ -11207,34 +11243,34 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>153</v>
+        <v>464</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>78</v>
+        <v>465</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11244,26 +11280,24 @@
         <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>134</v>
+        <v>467</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>261</v>
+        <v>468</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11312,7 +11346,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>158</v>
+        <v>466</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11324,16 +11358,16 @@
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>78</v>
+        <v>471</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>153</v>
+        <v>472</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11344,14 +11378,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11364,26 +11398,22 @@
         <v>78</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -11407,13 +11437,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>78</v>
+        <v>477</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11431,7 +11461,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11443,16 +11473,16 @@
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>132</v>
+        <v>479</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11461,12 +11491,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11477,10 +11507,10 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>78</v>
@@ -11489,13 +11519,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>149</v>
+        <v>481</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11546,13 +11576,13 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
@@ -11561,10 +11591,10 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>484</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>498</v>
+        <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>132</v>
@@ -11578,10 +11608,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11598,26 +11628,30 @@
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>317</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="R82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11661,7 +11695,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11679,7 +11713,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>132</v>
@@ -11693,10 +11727,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11707,7 +11741,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11719,13 +11753,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>352</v>
+        <v>186</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11752,13 +11786,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>78</v>
+        <v>495</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11776,13 +11810,13 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
@@ -11794,7 +11828,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>132</v>
@@ -11808,10 +11842,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11822,7 +11856,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11834,13 +11868,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>352</v>
+        <v>436</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11891,25 +11925,25 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>499</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>509</v>
+        <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>132</v>
@@ -11923,10 +11957,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11937,7 +11971,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -11949,13 +11983,13 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>511</v>
+        <v>150</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>512</v>
+        <v>151</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11982,13 +12016,13 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>513</v>
+        <v>78</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>514</v>
+        <v>78</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
@@ -12006,28 +12040,28 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>510</v>
+        <v>152</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>515</v>
+        <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12038,21 +12072,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12064,15 +12098,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>517</v>
+        <v>261</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12097,13 +12133,13 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -12121,19 +12157,19 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>516</v>
+        <v>158</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12142,7 +12178,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12153,14 +12189,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12173,24 +12209,26 @@
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>428</v>
+        <v>134</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>522</v>
+        <v>446</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>523</v>
+        <v>447</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12238,7 +12276,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>521</v>
+        <v>448</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12250,16 +12288,16 @@
         <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>526</v>
+        <v>132</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12270,10 +12308,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12299,10 +12337,10 @@
         <v>149</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>150</v>
+        <v>504</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>151</v>
+        <v>505</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12353,7 +12391,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>152</v>
+        <v>503</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12365,16 +12403,16 @@
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>78</v>
+        <v>506</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12385,21 +12423,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12411,17 +12449,15 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>261</v>
+        <v>508</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12470,19 +12506,19 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>158</v>
+        <v>507</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -12491,7 +12527,7 @@
         <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12502,46 +12538,42 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>134</v>
+        <v>360</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>438</v>
+        <v>511</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12589,25 +12621,25 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>440</v>
+        <v>510</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>78</v>
+        <v>513</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>132</v>
@@ -12621,10 +12653,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12647,13 +12679,13 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12704,7 +12736,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12722,10 +12754,10 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>358</v>
+        <v>132</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12736,10 +12768,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12750,7 +12782,7 @@
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12762,13 +12794,13 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>535</v>
+        <v>186</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12795,13 +12827,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -12819,13 +12851,13 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>78</v>
@@ -12837,10 +12869,10 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>539</v>
+        <v>132</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -12851,10 +12883,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12877,13 +12909,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>319</v>
+        <v>186</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12910,13 +12942,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>78</v>
+        <v>528</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12934,7 +12966,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12952,10 +12984,10 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>543</v>
+        <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>544</v>
+        <v>132</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12964,12 +12996,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12983,7 +13015,7 @@
         <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>78</v>
@@ -12992,15 +13024,17 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13049,7 +13083,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13067,10 +13101,10 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>132</v>
+        <v>534</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13081,10 +13115,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13196,10 +13230,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13313,14 +13347,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13342,10 +13376,10 @@
         <v>134</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>219</v>
@@ -13400,7 +13434,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13432,10 +13466,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13458,13 +13492,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>149</v>
+        <v>360</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13491,11 +13525,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13513,7 +13549,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13531,10 +13567,10 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>132</v>
+        <v>366</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13545,10 +13581,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13571,13 +13607,13 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>389</v>
+        <v>543</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13628,7 +13664,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13646,10 +13682,10 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>78</v>
+        <v>546</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>132</v>
+        <v>547</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13660,10 +13696,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13674,7 +13710,7 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13686,13 +13722,13 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>186</v>
+        <v>317</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13719,13 +13755,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>561</v>
+        <v>78</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>562</v>
+        <v>78</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13743,13 +13779,13 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
@@ -13761,10 +13797,10 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>132</v>
+        <v>552</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13773,12 +13809,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13786,13 +13822,13 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>78</v>
@@ -13801,17 +13837,15 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>564</v>
+        <v>436</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13848,23 +13882,25 @@
         <v>78</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AC101" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
@@ -13888,16 +13924,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13909,7 +13943,7 @@
         <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>78</v>
@@ -13918,17 +13952,15 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>571</v>
+        <v>149</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>572</v>
+        <v>150</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13977,10 +14009,10 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>563</v>
+        <v>152</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>89</v>
@@ -13989,7 +14021,7 @@
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -13998,7 +14030,7 @@
         <v>78</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -14009,21 +14041,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14035,16 +14067,16 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>564</v>
+        <v>134</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>574</v>
+        <v>261</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>575</v>
+        <v>262</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>567</v>
+        <v>219</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14094,38 +14126,851 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y105" s="2"/>
+      <c r="Z105" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AG103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
+      <c r="M108" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AC108" s="2"/>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AK108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AN103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO103" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO110" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO103">
+  <autoFilter ref="A1:AO110">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14135,7 +14980,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI102">
+  <conditionalFormatting sqref="A2:AI109">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
